--- a/ServiceWA/rf-config/MobileConfig.xlsx
+++ b/ServiceWA/rf-config/MobileConfig.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\snatarajan\Desktop\Sundar\ServiceWAMobile\ServiceWA\ServiceWA\rf-config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\snatarajan\PycharmProjects\ServiceWA_RF\ServiceWA\rf-config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1323CF2D-C632-4C21-BC3B-4B342610F3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA78F8FC-356E-4AA7-98F3-8C3F4F641B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23010" windowHeight="13410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="89">
   <si>
     <t>Mobile</t>
   </si>
@@ -299,7 +299,7 @@
     <t>iPhone 16 Pro</t>
   </si>
   <si>
-    <t>Samsung Galaxy S25</t>
+    <t>Samsung Galaxy S23</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1220,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.25" style="1" bestFit="1" customWidth="1"/>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>0</v>
@@ -2602,6 +2602,27 @@
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2" t="s">
         <v>74</v>
       </c>
     </row>
